--- a/03_BOM/BE-PC_EXP_V100_18DEC.xlsx
+++ b/03_BOM/BE-PC_EXP_V100_18DEC.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="G:\My Drive\Private\New folder (2)\16_BEE-PC_EXP\NANORACK_4U_EXP\03_BOM\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\1_AltiumProject\17_BEE_PC_EXP_V100\baobuibk-NANORACK_4U_EXP_HW_1.0.0\03_BOM\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A6CFB90-7D06-482B-8223-4C67528F6642}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8538EBFA-396D-438C-9AE6-63BDBA61A22C}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13176" xr2:uid="{BC06F63D-CF53-4F25-8084-601D2BD97FAB}"/>
   </bookViews>
